--- a/tests/fixtures/m0/icici_holdings_sample.xlsx
+++ b/tests/fixtures/m0/icici_holdings_sample.xlsx
@@ -485,15 +485,11 @@
           <t>Equity &amp; Equity Related Instruments (Note -1)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>6180420.349999999</v>
+        <v>1140638.3</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7124365864748</v>
+        <v>0.7476952532518614</v>
       </c>
     </row>
     <row r="6">
@@ -502,17 +498,12 @@
           <t>Listed / Awaiting Listing On Stock Exchanges</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>6063710.099999999</v>
+        <v>1140638.3</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6989883870219</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>0.7476952532518614</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -525,7 +516,6 @@
           <t>INE040A01034</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Banks</t>
@@ -538,9 +528,8 @@
         <v>517716.37</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0596550260489</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
+        <v>0.3393661885452947</v>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -553,7 +542,6 @@
           <t>INE090A01021</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Banks</t>
@@ -566,9 +554,8 @@
         <v>326277.54</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0375960589151</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>0.2138768862142314</v>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -581,7 +568,6 @@
           <t>INE002A01018</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Petroleum Products</t>
@@ -594,9 +580,8 @@
         <v>296644.39</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0341815129637</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>0.1944521784923353</v>
+      </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
@@ -604,17 +589,12 @@
           <t>TREPS</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
         <v>162641.02</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0187406751011</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>0.1066121649939697</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -622,17 +602,12 @@
           <t>Net Current Assets</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
         <v>222259.7215268232</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02561037325770825</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>0.1456925817541689</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -640,17 +615,12 @@
           <t>Total Net Assets</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>8678503.795731621</v>
+        <v>1525539.041526823</v>
       </c>
       <c r="H12" t="n">
         <v>0.9999999999896085</v>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
